--- a/data/market_excel/market_final_GST.xlsx
+++ b/data/market_excel/market_final_GST.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,67 +421,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>기업명</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>투자의견</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>총점</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>거시환경</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>산업매력도</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>경쟁위치</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>정책수혜</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>시장모멘텀</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>요약</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>밸류체인 위치</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>직접생산</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>플랫폼기업</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>데이터신뢰도</t>
         </is>
@@ -533,26 +521,10 @@
           <t>GST는 AI·HBM 시장 성장과 정부 정책 지원에 힘입어 긍정적인 산업 전망을 가지고 있습니다. 그러나 삼성전자 파업 및 거시 경제 불확실성으로 인한 단기적인 시장 모멘텀 약화는 보유 의견의 근거입니다.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>장비</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -569,47 +541,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>기업명</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>투자의견</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>총점</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>거시환경</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>산업매력도</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>경쟁위치</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>정책수혜</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>시장모멘텀</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>요약</t>
         </is>
@@ -665,62 +637,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>vc_role</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>direct_flag</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>platform_flag</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>domestic_peers</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>global_peers</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>competition_intensity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>differentiation</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>evidence_summary</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>rcept_no</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
@@ -729,7 +701,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>후공정/패키징/테스트</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -751,7 +723,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>당사는 반도체 및 디스플레이 제조 공정에서 사용되는 가스 정화 장비와 온도 조절 장비를 전문적으로 제조합니다. 이는 반도체 공정의 효율을 극대화하는데 기여합니다.</t>
+          <t>세계 유수의 반도체 업체들에게 최첨단 반도체 패키징 솔루션을 제공하여 업계에서 신뢰받는 기업으로 자리 잡고 있습니다.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -761,22 +733,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>사업보고서에 따르면, 주요 사업 내용으로 반도체 제조 공정에 사용되는 장비인 Scrubber와 Chiller를 제조한다고 명시되어 있습니다.</t>
+          <t>사업 개요에서 반도체 조립 및 테스트 제품을 주력으로 생산하고 있다고 명시되어 있습니다.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20241114000193</t>
+          <t>20241113000459</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-05-20T12:44:21.537862</t>
+          <t>2026-05-25T11:09:12.756789</t>
         </is>
       </c>
     </row>
@@ -795,37 +767,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>peer_group</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>domestic_peers</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>global_peers</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>competition_intensity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>differentiation</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
@@ -875,37 +847,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -935,7 +907,7 @@
         <v>180.5</v>
       </c>
       <c r="G2" t="n">
-        <v>134.8</v>
+        <v>143.9</v>
       </c>
     </row>
     <row r="3">
@@ -950,19 +922,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>533.7</v>
+        <v>528.8</v>
       </c>
       <c r="D3" t="n">
-        <v>619.5</v>
+        <v>680.1</v>
       </c>
       <c r="E3" t="n">
-        <v>548.6</v>
+        <v>556.6</v>
       </c>
       <c r="F3" t="n">
-        <v>795.3</v>
+        <v>683.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1896.6</v>
+        <v>1913.6</v>
       </c>
     </row>
     <row r="4">
@@ -983,13 +955,13 @@
         <v>293.4</v>
       </c>
       <c r="E4" t="n">
-        <v>224.9</v>
+        <v>224.8</v>
       </c>
       <c r="F4" t="n">
-        <v>495.2</v>
+        <v>455.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1885.4</v>
+        <v>1527.9</v>
       </c>
     </row>
     <row r="5">
@@ -1016,7 +988,7 @@
         <v>102.3</v>
       </c>
       <c r="G5" t="n">
-        <v>115.6</v>
+        <v>123.3</v>
       </c>
     </row>
     <row r="6">
@@ -1037,13 +1009,13 @@
         <v>406</v>
       </c>
       <c r="E6" t="n">
-        <v>500.7</v>
+        <v>481</v>
       </c>
       <c r="F6" t="n">
-        <v>429.9</v>
+        <v>464.2</v>
       </c>
       <c r="G6" t="n">
-        <v>551.3</v>
+        <v>469.4</v>
       </c>
     </row>
     <row r="7">
@@ -1088,16 +1060,16 @@
         <v>665</v>
       </c>
       <c r="D8" t="n">
-        <v>570</v>
+        <v>578.8</v>
       </c>
       <c r="E8" t="n">
-        <v>548.6</v>
+        <v>533.8</v>
       </c>
       <c r="F8" t="n">
         <v>605.9</v>
       </c>
       <c r="G8" t="n">
-        <v>851.1</v>
+        <v>750.7</v>
       </c>
     </row>
     <row r="9">
@@ -1115,16 +1087,16 @@
         <v>520</v>
       </c>
       <c r="D9" t="n">
-        <v>577.1</v>
+        <v>602.6</v>
       </c>
       <c r="E9" t="n">
-        <v>602.9</v>
+        <v>631</v>
       </c>
       <c r="F9" t="n">
-        <v>722.9</v>
+        <v>727.8</v>
       </c>
       <c r="G9" t="n">
-        <v>832</v>
+        <v>822.4</v>
       </c>
     </row>
     <row r="10">
@@ -1151,7 +1123,7 @@
         <v>61.5</v>
       </c>
       <c r="G10" t="n">
-        <v>70.3</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="11">
@@ -1169,16 +1141,16 @@
         <v>566.1</v>
       </c>
       <c r="D11" t="n">
-        <v>551.6</v>
+        <v>558.4</v>
       </c>
       <c r="E11" t="n">
-        <v>473.6</v>
+        <v>507.1</v>
       </c>
       <c r="F11" t="n">
-        <v>676.1</v>
+        <v>675</v>
       </c>
       <c r="G11" t="n">
-        <v>803.6</v>
+        <v>807.1</v>
       </c>
     </row>
     <row r="12">
@@ -1223,16 +1195,16 @@
         <v>481.6</v>
       </c>
       <c r="D13" t="n">
-        <v>483.4</v>
+        <v>490.2</v>
       </c>
       <c r="E13" t="n">
-        <v>535.7</v>
+        <v>533.5</v>
       </c>
       <c r="F13" t="n">
-        <v>681.1</v>
+        <v>650.8</v>
       </c>
       <c r="G13" t="n">
-        <v>796.7</v>
+        <v>796.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/market_excel/market_final_GST.xlsx
+++ b/data/market_excel/market_final_GST.xlsx
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,67 +433,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>기업명</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>투자의견</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>총점</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>거시환경</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>산업매력도</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>경쟁위치</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>정책수혜</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>시장모멘텀</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>요약</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>밸류체인 위치</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>직접생산</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>플랫폼기업</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>데이터신뢰도</t>
         </is>
@@ -541,47 +553,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>기업명</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>투자의견</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>총점</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>거시환경</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>산업매력도</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>경쟁위치</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>정책수혜</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>시장모멘텀</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>요약</t>
         </is>
@@ -637,62 +649,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>vc_role</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>direct_flag</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>platform_flag</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>domestic_peers</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>global_peers</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>competition_intensity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>differentiation</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>evidence_summary</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>rcept_no</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
@@ -767,37 +779,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>peer_group</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>domestic_peers</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>global_peers</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>competition_intensity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>differentiation</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
@@ -847,37 +859,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
